--- a/InputData/indst/NIEAFSM/New Indst Eqpt Alt Fuel Shifting Matrix.xlsx
+++ b/InputData/indst/NIEAFSM/New Indst Eqpt Alt Fuel Shifting Matrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanO'Brien\Models\EPS\US\eps-us\InputData\indst\NIEAFSM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\NIEAFSM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02F4CF2-972E-4B08-916D-441CC74BFA6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4BA46FB-7811-43B6-BAA2-0D727438DAA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22845" yWindow="465" windowWidth="22590" windowHeight="14040" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" xr2:uid="{CEBBDD15-8244-44C2-A2EB-EB506D69E415}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="29">
   <si>
     <t>Source:</t>
   </si>
@@ -76,12 +76,6 @@
     <t>LPG propane or butane if</t>
   </si>
   <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
-  </si>
-  <si>
     <t>RHIFUbSL Recipient Hydrogen Industrial Fuel Used by Shifting Lever</t>
   </si>
   <si>
@@ -94,9 +88,6 @@
     <t>This can be used to represent, for example, a shift to the use of</t>
   </si>
   <si>
-    <t>green hydrogen for high-temperature heat applications or a shift</t>
-  </si>
-  <si>
     <t xml:space="preserve">from coal to natural gas in specific applications. </t>
   </si>
   <si>
@@ -128,6 +119,9 @@
   </si>
   <si>
     <t xml:space="preserve">Each row and column must sum to one. </t>
+  </si>
+  <si>
+    <t>hydrogen for high-temperature heat applications or a shift</t>
   </si>
 </sst>
 </file>
@@ -530,7 +524,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -548,72 +542,72 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -632,16 +626,16 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.5703125" customWidth="1"/>
-    <col min="2" max="13" width="12" customWidth="1"/>
+    <col min="2" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" s="2" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>4</v>
@@ -673,14 +667,8 @@
       <c r="K1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -714,14 +702,8 @@
       <c r="K2" s="4">
         <v>0</v>
       </c>
-      <c r="L2" s="4">
-        <v>0</v>
-      </c>
-      <c r="M2" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -753,16 +735,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
         <v>1</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -794,16 +770,10 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
         <v>1</v>
       </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -835,16 +805,10 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
         <v>1</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -876,16 +840,10 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
         <v>1</v>
       </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -919,14 +877,8 @@
       <c r="K7" s="4">
         <v>0</v>
       </c>
-      <c r="L7" s="4">
-        <v>0</v>
-      </c>
-      <c r="M7" s="4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -958,16 +910,10 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
         <v>1</v>
       </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -999,16 +945,10 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
         <v>1</v>
       </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -1040,16 +980,10 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
         <v>1</v>
       </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
@@ -1081,95 +1015,7 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
         <v>1</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="4">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>1</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="4">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>1</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
